--- a/output/supplementary/P3_Fig3D_sunburst_data.xlsx
+++ b/output/supplementary/P3_Fig3D_sunburst_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -901,17 +901,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>PMA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prospective</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Predicate</t>
+          <t>Radiologist</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -921,37 +921,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>PMA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Retrospective</t>
+          <t>Not described</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>None/NR</t>
+          <t>Predicate</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>PMA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Retrospective</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Predicate</t>
+          <t>None/NR</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -966,12 +966,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Radiologist</t>
+          <t>Predicate</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -986,16 +986,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Not described</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Predicate</t>
+          <t>Radiologist</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1006,75 +1006,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Prospective</t>
+          <t>Retrospective</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>None/NR</t>
+          <t>Radiologist</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PMA</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Prospective</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Predicate</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PMA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Prospective</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Radiologist</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>PMA</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Retrospective</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Radiologist</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
         <v>2</v>
       </c>
     </row>
